--- a/d/2026-08-19_会员有效性分析.xlsx
+++ b/d/2026-08-19_会员有效性分析.xlsx
@@ -5591,30 +5591,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>155****8549</t>
+          <t>159****9981</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>APR北京大族广场</t>
+          <t>APR成都三利爱琴海、APR成都天府大悦城、APR成都天府环宇坊、APR成都高新伊藤</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>153****2023</t>
+          <t>136****4467</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5625,42 +5625,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>APR北京西铁营万达</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>159****9981</t>
+          <t>153****2023</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>APR成都三利爱琴海、APR成都天府大悦城、APR成都天府环宇坊、APR成都高新伊藤</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>136****4467</t>
+          <t>155****8549</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>APR北京西铁营万达</t>
+          <t>APR北京大族广场</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5706,7 +5706,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>182****5124</t>
+          <t>182****5317</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>华为北京牡丹园翠微</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5729,7 +5729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>182****5317</t>
+          <t>182****5124</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京牡丹园翠微</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5821,7 +5821,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>132****9486</t>
+          <t>131****2308</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>华为北京丽泽龙湖</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5844,7 +5844,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>139****2920</t>
+          <t>177****7547</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>华为北京槐房万达</t>
+          <t>华为北京牡丹园翠微</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5890,7 +5890,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>186****1441</t>
+          <t>137****2823</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5901,19 +5901,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京芳草地概念店</t>
+          <t>华为福州东街口</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>159****4633</t>
+          <t>136****2939</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5924,19 +5924,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>DJI北京中关村大融城授权体验店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>173****1817</t>
+          <t>139****2920</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5959,7 +5959,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>152****1055</t>
+          <t>159****4633</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5970,19 +5970,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>APR成都科华王府井</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>四川新跃</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>131****2308</t>
+          <t>185****1711</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>华为北京来福士</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -6005,7 +6005,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>137****7690</t>
+          <t>186****1441</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DJI北京万柳华联授权体验店</t>
+          <t>DJI大疆哈苏北京芳草地概念店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -6028,7 +6028,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>185****1711</t>
+          <t>152****1055</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6039,19 +6039,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>华为北京来福士</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>136****4521</t>
+          <t>173****1817</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>华为北京丽泽龙湖</t>
+          <t>华为北京槐房万达</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -6074,7 +6074,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>177****7547</t>
+          <t>136****4521</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>华为北京牡丹园翠微</t>
+          <t>华为北京丽泽龙湖</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -6097,7 +6097,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>137****2823</t>
+          <t>132****9486</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6108,19 +6108,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>华为福州东街口</t>
+          <t>华为北京丽泽龙湖</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>136****2939</t>
+          <t>137****7690</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DJI北京中关村大融城授权体验店</t>
+          <t>DJI北京万柳华联授权体验店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6143,7 +6143,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>139****6069</t>
+          <t>186****6630</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6154,19 +6154,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>华为北京汇琴广场</t>
+          <t>DJI大疆哈苏北京朝阳合生汇概念店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>185****1969</t>
+          <t>138****2828</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6177,19 +6177,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>DJI北京万柳华联授权体验店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>186****6630</t>
+          <t>188****2372</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -6200,19 +6200,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京朝阳合生汇概念店</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>186****7532</t>
+          <t>138****7767</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -6223,19 +6223,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>APR北京昌发展万科</t>
+          <t>APR成都环球中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>135****4397</t>
+          <t>139****3525</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -6246,19 +6246,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>APR成都西宸天街</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>151****9553</t>
+          <t>139****0365</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>华为北京上德银泰</t>
+          <t>华为北京东坝万达</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6281,7 +6281,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>158****8090</t>
+          <t>134****8604</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>华为北京丽泽龙湖</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6304,7 +6304,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>136****0388</t>
+          <t>135****5965</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -6315,19 +6315,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京大兴机场概念店</t>
+          <t>DJI上海久光中心授权体验店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>186****5703</t>
+          <t>186****7532</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>APR北京西三旗万象汇</t>
+          <t>APR北京昌发展万科</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -6350,7 +6350,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>186****1299</t>
+          <t>139****3924</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -6373,7 +6373,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>138****8165</t>
+          <t>186****9663</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -6384,19 +6384,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>APR北京旧宫万科</t>
+          <t>DJI上海静安大悦城授权体验店</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>188****2372</t>
+          <t>188****0838</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -6407,19 +6407,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>APR成都时代天街</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>157****6719</t>
+          <t>136****3198</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -6430,19 +6430,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>APR北京房山龙湖</t>
+          <t>华为北京来福士</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>152****7644</t>
+          <t>139****7792</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DJI北京昌平悦荟授权体验店</t>
+          <t>DJI北京西北旺万象汇授权体验店</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -6465,7 +6465,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>136****7960</t>
+          <t>136****4463</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -6476,19 +6476,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DJI上海久光中心授权体验店</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>188****8341</t>
+          <t>139****3980</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>APR北京大族广场</t>
+          <t>APR北京槐房万达</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6511,7 +6511,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>139****1328</t>
+          <t>185****7001</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>华为北京首开万象汇</t>
+          <t>华为北京丰科万达</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6534,7 +6534,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>136****0510</t>
+          <t>157****5741</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -6545,19 +6545,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>华为厦门思明加州广场</t>
+          <t>DJI北京金源购物广场授权体验店</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>188****0838</t>
+          <t>135****7736</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -6568,19 +6568,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>APR成都时代天街</t>
+          <t>华为北京来福士</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>139****0365</t>
+          <t>139****6069</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>华为北京东坝万达</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6603,7 +6603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>186****9663</t>
+          <t>135****0505</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -6614,19 +6614,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DJI上海静安大悦城授权体验店</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>139****0032</t>
+          <t>150****3076</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -6637,19 +6637,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>APR北京石景山喜隆多</t>
+          <t>华为北京通州乐堤港</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>139****7792</t>
+          <t>151****9553</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -6660,19 +6660,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DJI北京西北旺万象汇授权体验店</t>
+          <t>华为北京上德银泰</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>139****3924</t>
+          <t>130****7661</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -6683,19 +6683,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>APR成都科华王府井</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>157****5741</t>
+          <t>186****2232</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DJI北京金源购物广场授权体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6718,7 +6718,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>186****7077</t>
+          <t>139****1328</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -6729,19 +6729,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DJI北京龙湖大兴天街授权体验店</t>
+          <t>华为北京首开万象汇</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>138****1917</t>
+          <t>176****6910</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>APR北京顺义华联</t>
+          <t>APR北京房山龙湖</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6764,7 +6764,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>177****0103</t>
+          <t>135****5842</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6787,7 +6787,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>195****9249</t>
+          <t>186****1299</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -6798,19 +6798,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DJI上海长宁龙之梦授权体验店</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>176****6910</t>
+          <t>134****5346</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>APR北京房山龙湖</t>
+          <t>APR北京颐堤港</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6833,7 +6833,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>156****7796</t>
+          <t>152****7644</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -6844,19 +6844,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>APR北京新奥天虹</t>
+          <t>DJI北京昌平悦荟授权体验店</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>134****8604</t>
+          <t>136****0510</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -6867,19 +6867,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为厦门思明加州广场</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>190****3712</t>
+          <t>139****5360</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>APR成都高新伊藤</t>
+          <t>APR成都环球中心</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6902,7 +6902,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>186****2232</t>
+          <t>135****4397</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -6913,19 +6913,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>136****3198</t>
+          <t>185****1031</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -6936,19 +6936,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>华为北京来福士</t>
+          <t>DJI北京中关村大融城授权体验店</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>136****4463</t>
+          <t>190****3712</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -6959,19 +6959,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>APR成都高新伊藤</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>135****5965</t>
+          <t>132****1018</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -6982,19 +6982,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DJI上海久光中心授权体验店</t>
+          <t>APR北京五棵松华熙</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>135****5842</t>
+          <t>130****7039</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>华为北京同成街华联</t>
+          <t>华为北京首开万象汇</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7017,7 +7017,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>158****7802</t>
+          <t>135****5632</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -7028,19 +7028,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>华为北京同成街华联</t>
+          <t>DJI北京万柳华联授权体验店</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>135****5980</t>
+          <t>172****0421</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DJI北京蓝色港湾授权体验店</t>
+          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7086,7 +7086,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>138****2828</t>
+          <t>188****8341</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -7097,19 +7097,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DJI北京万柳华联授权体验店</t>
+          <t>APR北京大族广场</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>135****0505</t>
+          <t>136****0388</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -7120,19 +7120,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>DJI大疆哈苏北京大兴机场概念店</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>153****2580</t>
+          <t>182****4467</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>华为北京平谷万达</t>
+          <t>华为北京亦庄龙湖</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7155,7 +7155,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>139****9313</t>
+          <t>150****8465</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>华为北京旧宫万科</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7178,7 +7178,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>135****5632</t>
+          <t>177****0103</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -7189,19 +7189,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DJI北京万柳华联授权体验店</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>166****4157</t>
+          <t>136****9791</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>华为北京旧宫万科</t>
+          <t>APR北京同成街华联</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>139****3525</t>
+          <t>157****6719</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -7258,19 +7258,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>APR成都西宸天街</t>
+          <t>APR北京房山龙湖</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>134****5346</t>
+          <t>133****5385</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -7281,19 +7281,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>APR北京颐堤港</t>
+          <t>DJI上海久光中心授权体验店</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>132****1018</t>
+          <t>166****4157</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -7304,19 +7304,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>APR北京五棵松华熙</t>
+          <t>华为北京旧宫万科</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>133****5385</t>
+          <t>158****7802</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -7327,19 +7327,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>DJI上海久光中心授权体验店</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>182****4467</t>
+          <t>135****5980</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -7350,19 +7350,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>华为北京亦庄龙湖</t>
+          <t>DJI北京蓝色港湾授权体验店</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>150****3076</t>
+          <t>158****8090</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>华为北京通州乐堤港</t>
+          <t>华为北京丽泽龙湖</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7385,7 +7385,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>138****7767</t>
+          <t>186****7077</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -7396,19 +7396,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>APR成都环球中心</t>
+          <t>DJI北京龙湖大兴天街授权体验店</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>150****8465</t>
+          <t>139****8881</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京牡丹园翠微</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7431,7 +7431,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>135****7736</t>
+          <t>153****2580</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>华为北京来福士</t>
+          <t>华为北京平谷万达</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7454,7 +7454,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>139****8881</t>
+          <t>136****7960</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -7465,19 +7465,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>华为北京牡丹园翠微</t>
+          <t>DJI上海久光中心授权体验店</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>130****7661</t>
+          <t>195****9249</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -7488,19 +7488,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>DJI上海长宁龙之梦授权体验店</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>上海爱飞</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>139****5360</t>
+          <t>134****7758</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>APR成都环球中心</t>
+          <t>APR成都北城天街</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7523,7 +7523,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>139****3980</t>
+          <t>139****0032</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>APR北京槐房万达</t>
+          <t>APR北京石景山喜隆多</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7546,7 +7546,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>136****9791</t>
+          <t>185****1969</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -7557,19 +7557,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>APR北京同成街华联</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>172****0421</t>
+          <t>139****9313</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -7580,19 +7580,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
+          <t>华为北京旧宫万科</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>134****7758</t>
+          <t>138****1917</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -7603,19 +7603,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>APR成都北城天街</t>
+          <t>APR北京顺义华联</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>185****7001</t>
+          <t>156****7796</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -7626,19 +7626,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>华为北京丰科万达</t>
+          <t>APR北京新奥天虹</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>185****1031</t>
+          <t>138****8165</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -7649,19 +7649,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DJI北京中关村大融城授权体验店</t>
+          <t>APR北京旧宫万科</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>130****7039</t>
+          <t>186****5703</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>华为北京首开万象汇</t>
+          <t>APR北京西三旗万象汇</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
@@ -7769,14 +7769,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>185****4346</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>1094</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -7795,14 +7795,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>185****4346</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="5">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>150****8465</t>
+          <t>134****8604</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>134****8604</t>
+          <t>150****8465</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>135****5965</t>
+          <t>136****7960</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>136****7960</t>
+          <t>135****5965</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>135****5632</t>
+          <t>138****2828</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>138****2828</t>
+          <t>135****5632</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>135****0505</t>
+          <t>136****4463</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>136****4463</t>
+          <t>177****0103</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>177****0103</t>
+          <t>135****0505</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>186****1299</t>
+          <t>188****2372</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>188****2372</t>
+          <t>186****1299</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>132****9486</t>
+          <t>136****4521</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>136****4521</t>
+          <t>132****9486</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>139****2920</t>
+          <t>173****1817</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>173****1817</t>
+          <t>139****2920</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -10135,14 +10135,14 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>137****2823</t>
         </is>
       </c>
       <c r="E94" t="n">
         <v>4</v>
       </c>
       <c r="F94" t="n">
-        <v>1094</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
@@ -10161,14 +10161,14 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>137****2823</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E95" t="n">
         <v>4</v>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="96">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>139****1328</t>
+          <t>130****7039</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>130****7039</t>
+          <t>139****1328</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>166****4157</t>
+          <t>139****9313</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>139****9313</t>
+          <t>166****4157</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -10993,14 +10993,14 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>186****7077</t>
         </is>
       </c>
       <c r="E127" t="n">
         <v>3</v>
       </c>
       <c r="F127" t="n">
-        <v>1094</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
@@ -11019,14 +11019,14 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>186****7077</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E128" t="n">
         <v>3</v>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="129">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>139****5360</t>
+          <t>138****7767</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>138****7767</t>
+          <t>139****5360</t>
         </is>
       </c>
       <c r="E134" t="n">
